--- a/questionnaire_templates/029_hepatobiliary_tumor_evaluation_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/029_hepatobiliary_tumor_evaluation_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_history_other</t>
+          <t>medical_history_other_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical History Other</t>
+          <t>Medical History Other 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tumor_characteristics_other</t>
+          <t>tumor_characteristics_other_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tumor Characteristics Other</t>
+          <t>Tumor Characteristics Other 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tumor_location_other</t>
+          <t>tumor_location_other_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tumor Location Other</t>
+          <t>Tumor Location Other 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>medical_history_others</t>
+          <t>medical_history_others_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical History Others</t>
+          <t>Medical History Others 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>medical_history_others</t>
+          <t>medical_history_others_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Medical History Others</t>
+          <t>Medical History Others 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medical_history_other_choices</t>
+          <t>medical_history_other_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medical_history_other_choices</t>
+          <t>medical_history_other_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>medical_history_other_choices</t>
+          <t>medical_history_other_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>medical_history_other_choices</t>
+          <t>medical_history_other_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_3_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>medical_history_others_choices</t>
+          <t>medical_history_others_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
